--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -534,7 +534,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|ServiceRequest)
 </t>
   </si>
   <si>
@@ -557,7 +557,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure|4.0.1|Observation|4.0.1|MedicationAdministration|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationadministration)
 </t>
   </si>
   <si>
@@ -785,7 +785,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -1006,7 +1006,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|Procedure|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
 </t>
   </si>
   <si>
@@ -1071,7 +1071,7 @@
     <t>Procedure.report</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|4.0.1|DocumentReference|4.0.1|Composition|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)
 </t>
   </si>
   <si>
@@ -1111,7 +1111,7 @@
     <t>Procedure.complicationDetail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition)
 </t>
   </si>
   <si>
@@ -1206,7 +1206,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device)
 </t>
   </si>
   <si>
@@ -1222,7 +1222,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Medication|4.0.1|Substance|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medication|Substance)
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-procedure.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
